--- a/artfynd/A 10439-2025 artfynd.xlsx
+++ b/artfynd/A 10439-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123992296</v>
+        <v>123991490</v>
       </c>
       <c r="B2" t="n">
-        <v>96957</v>
+        <v>100257</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,37 +691,42 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221945</v>
+        <v>222498</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Långmossen, Långmossen, Srm</t>
+          <t>Långmossen, Srm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>626103</v>
+        <v>626092</v>
       </c>
       <c r="R2" t="n">
-        <v>6562229</v>
+        <v>6562135</v>
       </c>
       <c r="S2" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -750,7 +755,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +765,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,10 +792,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123991490</v>
+        <v>123992296</v>
       </c>
       <c r="B3" t="n">
-        <v>100257</v>
+        <v>96957</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,42 +808,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>222498</v>
+        <v>221945</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Långmossen, Srm</t>
+          <t>Långmossen, Långmossen, Srm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>626092</v>
+        <v>626103</v>
       </c>
       <c r="R3" t="n">
-        <v>6562135</v>
+        <v>6562229</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -867,7 +867,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -877,7 +877,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AD3" t="b">

--- a/artfynd/A 10439-2025 artfynd.xlsx
+++ b/artfynd/A 10439-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123991490</v>
+        <v>123992296</v>
       </c>
       <c r="B2" t="n">
-        <v>100279</v>
+        <v>96979</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,42 +691,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>222498</v>
+        <v>221945</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Långmossen, Srm</t>
+          <t>Långmossen, Långmossen, Srm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>626092</v>
+        <v>626103</v>
       </c>
       <c r="R2" t="n">
-        <v>6562135</v>
+        <v>6562229</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -755,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -765,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -792,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123992296</v>
+        <v>123991490</v>
       </c>
       <c r="B3" t="n">
-        <v>96979</v>
+        <v>100279</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -808,37 +803,42 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221945</v>
+        <v>222498</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Långmossen, Långmossen, Srm</t>
+          <t>Långmossen, Srm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>626103</v>
+        <v>626092</v>
       </c>
       <c r="R3" t="n">
-        <v>6562229</v>
+        <v>6562135</v>
       </c>
       <c r="S3" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -867,7 +867,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -877,7 +877,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AD3" t="b">

--- a/artfynd/A 10439-2025 artfynd.xlsx
+++ b/artfynd/A 10439-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123992296</v>
+        <v>123991490</v>
       </c>
       <c r="B2" t="n">
-        <v>96979</v>
+        <v>100279</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,37 +691,42 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221945</v>
+        <v>222498</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Långmossen, Långmossen, Srm</t>
+          <t>Långmossen, Srm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>626103</v>
+        <v>626092</v>
       </c>
       <c r="R2" t="n">
-        <v>6562229</v>
+        <v>6562135</v>
       </c>
       <c r="S2" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -750,7 +755,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +765,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,10 +792,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123991490</v>
+        <v>123992296</v>
       </c>
       <c r="B3" t="n">
-        <v>100279</v>
+        <v>96979</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,42 +808,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>222498</v>
+        <v>221945</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Långmossen, Srm</t>
+          <t>Långmossen, Långmossen, Srm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>626092</v>
+        <v>626103</v>
       </c>
       <c r="R3" t="n">
-        <v>6562135</v>
+        <v>6562229</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -867,7 +867,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -877,7 +877,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AD3" t="b">
